--- a/AAII_Financials/Quarterly/PINS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PINS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="92">
   <si>
     <t>PINS</t>
   </si>
@@ -656,467 +656,480 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1179700</v>
+      </c>
+      <c r="E8" s="3">
         <v>1007500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1319300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1049200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>998200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>855000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1154100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>898400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>853700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>740000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>981300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>763200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>708000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>602600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>877200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>684600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>665900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>574900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>846700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>632900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>613200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>485200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>705600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>442600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>272500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>271900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>399900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>279700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>261200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>201900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>273200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>190200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>161200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>131400</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>257400</v>
+      </c>
+      <c r="E9" s="3">
         <v>238600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>226900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>212300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>203000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>199300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>197000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>187500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>184900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>181100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>178100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>171000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>168700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>170900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>185000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>182600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>164900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>146100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>141200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>126800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>127800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>133500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>129000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>112800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>108300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>99200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>96300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>83500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>105400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>73700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>68300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>63600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>58000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>51700</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>922300</v>
+      </c>
+      <c r="E10" s="3">
         <v>769000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1092400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>836900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>795200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>655700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>957200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>710900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>668800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>558900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>803200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>592200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>539300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>431700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>692200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>502000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>501000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>428800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>705500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>506100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>485400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>351700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>576600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>329800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>164200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>172700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>303600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>196200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>155800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>128200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>204900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>126600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>103200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>79700</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,112 +1166,116 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>451000</v>
+      </c>
+      <c r="E12" s="3">
         <v>380800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>364900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>371300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>359600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>331700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>320800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>326700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>312800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>280300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>268000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>264700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>269400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>266300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>265200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>254700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>233500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>195500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>240900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>185900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>181700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>171700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>163700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>160200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>136600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>145700</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>165000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>167700</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>801900</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>72400</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>66500</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>63500</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>61600</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1361,17 +1378,20 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E14" s="3">
         <v>47100</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>34</v>
       </c>
@@ -1381,23 +1401,23 @@
       <c r="H14" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>34700</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>34</v>
+      <c r="M14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>34</v>
@@ -1405,12 +1425,12 @@
       <c r="P14" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="R14" s="3">
         <v>11100</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>34</v>
       </c>
@@ -1426,8 +1446,8 @@
       <c r="W14" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1465,53 +1485,56 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E15" s="3">
         <v>7400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>6000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>7200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>6100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>5800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>6100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5400</v>
-      </c>
-      <c r="K15" s="3">
-        <v>4900</v>
       </c>
       <c r="L15" s="3">
         <v>4900</v>
       </c>
       <c r="M15" s="3">
+        <v>4900</v>
+      </c>
+      <c r="N15" s="3">
         <v>5300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>4900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>5100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>6200</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1569,8 +1592,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1630,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>1220500</v>
+      </c>
+      <c r="E17" s="3">
         <v>1040700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1018200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>990700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1002600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>890500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>892500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>869600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>875100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>794400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>785000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>768200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>781300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>846300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>871300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>753900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>700400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>578600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>667200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>534500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>542000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>508100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>500500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>539600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>377000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>418000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>443100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>413400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1428400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>246700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>229100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>212600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>202600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>186300</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-40900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-33200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>301200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>58500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-4300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-35500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>261600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>28700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-21400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-54400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>196300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-5000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-73200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-243700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>5900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-69300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-34500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-3600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>179500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>98400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>71200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-22900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>205100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-97000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-104500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-146100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-43200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-133700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-1167200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-44800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>44100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-22400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-41400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-54900</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1850,216 +1883,223 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E20" s="3">
         <v>1000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-11000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-4500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>13300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>4600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>4500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-5900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>4600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>22900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-5900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-2700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-4000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1500</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>3400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>4200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>5100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>8000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>8800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>7700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>3600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>3100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>3600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>3000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-31900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-26800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>307100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>65900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>12700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-25100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>254300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>37400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-21100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-54100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>207500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-4700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-66000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-237200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>48400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-59600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-31300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>184000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>101200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>79400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-16200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>216300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-85200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-91800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-129300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-26900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-117600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-1153000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-35600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>52700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-13700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-32900</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-47800</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -2102,8 +2142,8 @@
       <c r="P22" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2162,216 +2202,225 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-49200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-63500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>327700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>87200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>34700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>276800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>29800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>8600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-27700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>231100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>17100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-46200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-218500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>28800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-70200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-40400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-4200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>176800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>94400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>72700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-23000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>208500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-94200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-100300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-141000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-35200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-124900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-1159500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-41300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>47200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-18800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-38400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-52600</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E24" s="3">
         <v>10100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>50600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-4900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-4100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-12600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1570600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-2900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>29900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>10400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-11200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-9900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>11300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-5000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>3200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>700</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
       <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
         <v>400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-200</v>
       </c>
-      <c r="AE24" s="3">
-        <v>0</v>
-      </c>
       <c r="AF24" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AG24" s="3">
         <v>200</v>
       </c>
       <c r="AH24" s="3">
+        <v>200</v>
+      </c>
+      <c r="AI24" s="3">
         <v>100</v>
       </c>
-      <c r="AI24" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2474,216 +2523,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-46700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-73600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>277100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>92100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>38800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>8900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1847500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>30600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>8900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-24800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>201200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>6700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-34900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-208600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>17500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-65200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-43100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-5300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>174700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>94000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>69400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-21700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>207800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-94200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-100700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-141200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-35700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-124700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-1159500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-41400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>47000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-18900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-38400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-52700</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-46700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-73600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>277100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>92100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>38800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>8900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1847500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>30600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>8900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-24800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>201200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>6700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-34900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-208600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>17500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-65200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-43100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-5300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>174700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>94000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>69400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-21700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>207800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-94200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-100700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-141200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-35700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-124700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-1159500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-41400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>47000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-18900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-38400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-52700</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2786,8 +2844,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2890,8 +2951,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2994,8 +3058,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3098,216 +3165,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>11000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>4500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-13300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-4600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-4500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>5900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-4600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-22900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>5900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>2700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>4000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1500</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-4200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-8000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-8800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-7700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-3600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-3100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-3600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>-46700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-73600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>277100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>92100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>38800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>8900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1847500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>30600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>8900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-24800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>201200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>6700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-34900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-208600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>17500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-65200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-43100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-5300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>174700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>94000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>69400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-21700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>207800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-94200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-100700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-141200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-35700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-124700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-1159500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-41400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>47000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-18900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-38400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-52700</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3410,221 +3486,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>-46700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-73600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>277100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>92100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>38800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>8900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1847500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>30600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>8900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-24800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>201200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>6700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-34900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-208600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>17500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-65200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-43100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-5300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>174700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>94000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>69400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-21700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>207800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-94200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-100700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-141200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-35700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-124700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-1159500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-41400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>47000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-18900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-38400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-52700</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3661,8 +3746,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3699,320 +3785,330 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>422500</v>
+      </c>
+      <c r="E41" s="3">
         <v>378100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>969300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1132400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1216900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1252300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1136500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1035600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1376700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1632100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1361900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1168400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1179900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1651200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1611100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1671300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1641500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1683800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1419600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1231900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1012900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>913700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>669200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>652700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>863600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>740800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>649700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1033900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1408700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>134600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>122500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>100100</v>
       </c>
-      <c r="AI41" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="AJ41" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="AK41" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>852400</v>
+      </c>
+      <c r="E42" s="3">
         <v>920500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1497800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1538900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1442400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1362900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1376400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1407000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1358500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1144300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1149100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1162300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1115600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1078500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1087200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>994200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1017500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>994300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1060500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1075500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1130400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1120000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1091100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>996400</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>839500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>995900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1063700</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>691900</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>442000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>507600</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>505300</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>554200</v>
       </c>
-      <c r="AI42" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="AJ42" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="AK42" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>932000</v>
+      </c>
+      <c r="E43" s="3">
         <v>830400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>997800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>800500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>760100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>710000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>893400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>680500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>664300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>563900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>763200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>624200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>544100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>488000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>681500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>511100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>511500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>473000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>653400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>505000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>468200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>389200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>563700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>339300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>209900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>212200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>316400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>210300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>203000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>161100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>221900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>138900</v>
       </c>
-      <c r="AI43" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="AJ43" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="AK43" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4055,8 +4151,8 @@
       <c r="P44" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4115,8 +4211,11 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4159,172 +4258,178 @@
       <c r="P45" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="R45" s="3">
         <v>74900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>85500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>75600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>56200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>48100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>58700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>52200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>34300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>33500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>44500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>45200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>32600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>37500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>46400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>52700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>43600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>39600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>38100</v>
       </c>
-      <c r="AI45" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="AJ45" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="AK45" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2323300</v>
+      </c>
+      <c r="E46" s="3">
         <v>2242700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3555700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3565400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3518400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3402300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3484700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3232400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3492700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3413800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3338600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3039300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2941100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3298400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3454700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3262100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3246100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3207400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3181600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2871100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2663700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2457200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2357500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2032900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1958200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1981500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2067200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1982500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2106400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>846900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>889400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>831200</v>
       </c>
-      <c r="AI46" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="AJ46" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="AK46" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4367,8 +4472,8 @@
       <c r="P47" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -4427,216 +4532,225 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>240500</v>
+      </c>
+      <c r="E48" s="3">
         <v>235500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>216900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>185300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>127700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>130700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>131500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>125600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>124000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>123200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>124300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>132300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>122000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>127900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>265800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>273200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>284400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>277500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>281300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>257500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>195900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>209500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>225300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>241100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>248300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>263300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>280200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>254700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>238200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>243800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>226700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>225800</v>
       </c>
-      <c r="AI48" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="AJ48" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="AK48" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>558300</v>
+      </c>
+      <c r="E49" s="3">
         <v>563100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>106300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>107400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>108600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>110200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>110100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>111900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>113800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>115600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>117500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>119300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>121100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>123000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>124800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>140100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>145700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>60100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>61100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>13600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>13800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>13300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>13600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>13800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>14100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>14300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>14600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>15000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>15400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>13700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>14100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>10600</v>
       </c>
-      <c r="AI49" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="AJ49" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="AK49" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4853,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,112 +4960,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E52" s="3">
         <v>22300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>21100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>18200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>17100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>14600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>13800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>21200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>17000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>14100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>11000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>13700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>17500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>17200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>17400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>16800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>17900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>13300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>13200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>10600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>12200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>12300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>13100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>13200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>29100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>29500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>31300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>28300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>27200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>36700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>22600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>22200</v>
       </c>
-      <c r="AI52" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="AJ52" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="AK52" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5174,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4759400</v>
+      </c>
+      <c r="E54" s="3">
         <v>4645300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5492100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5515400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5403000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5282700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5342700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3491100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3747500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3666700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3594400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3304600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3201800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3566400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3862700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3692200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3694000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3558200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3537200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3152800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2885600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2692300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2609500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2301000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2249600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2288600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2393300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2280500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2387200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1141200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1152700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1089800</v>
       </c>
-      <c r="AI54" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="AJ54" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="AK54" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5322,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,112 +5361,116 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>145100</v>
+      </c>
+      <c r="E57" s="3">
         <v>75000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>129800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>90600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>91900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>96700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>84000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>88900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>73900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>83700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>79100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>71500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>64100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>77300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>87900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>88600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>57900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>12500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>17700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>57600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>48000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>48600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>49500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>41700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>43700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>37700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>34300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>31500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>30500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>30300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>22200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>21400</v>
       </c>
-      <c r="AI57" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="AJ57" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="AK57" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5344,11 +5478,11 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>41400</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
         <v>0</v>
       </c>
@@ -5356,11 +5490,11 @@
         <v>0</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>34400</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
@@ -5368,11 +5502,11 @@
         <v>0</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>35700</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
         <v>0</v>
       </c>
@@ -5439,261 +5573,270 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E59" s="3">
+      <c r="D59" s="3">
+        <v>93500</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F59" s="3">
         <v>47500</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="G59" s="3" t="s">
         <v>34</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="I59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J59" s="3">
         <v>23400</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>34</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="N59" s="3">
         <v>15300</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>34</v>
       </c>
       <c r="P59" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="R59" s="3">
         <v>292600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>256100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>292900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>213000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>242100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>183400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>189400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>160400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>155300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>147900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>122900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>133100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>141800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>112700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>109400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>93200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>86300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>76500</v>
       </c>
-      <c r="AI59" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="AJ59" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="AK59" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>609800</v>
+      </c>
+      <c r="E60" s="3">
         <v>530800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>465500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>426300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>401800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>404400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>398100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>409300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>367700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>339900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>317100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>304300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>319900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>321900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>380500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>344700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>350900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>225600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>259800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>241000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>237400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>209000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>204800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>189600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>166600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>170800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>176200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>144200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>139900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>123500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>108400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>97900</v>
       </c>
-      <c r="AI60" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="AJ60" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="AK60" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1196600</v>
+      </c>
+      <c r="E61" s="3">
         <v>1205000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>220600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>205200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>137400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>144000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>151400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>154400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>151800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>154300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>160600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>170900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>163000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>159500</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -5751,112 +5894,118 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>59000</v>
+      </c>
+      <c r="E62" s="3">
         <v>58900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>60800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>58900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>51800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>45900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>42000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>33600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>30000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>28700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>26000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>22700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>25800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>25300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>200500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>203000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>207100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>233000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>238700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>213400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>144300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>154500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>162300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>176800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>176400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>179300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>193500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>179900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>174000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>186300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>173500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>170500</v>
       </c>
-      <c r="AI62" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="AJ62" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="AK62" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6108,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6063,8 +6215,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6322,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1865500</v>
+      </c>
+      <c r="E66" s="3">
         <v>1794700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>746900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>690400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>591000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>594200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>591500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>597300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>549500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>522900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>503700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>497900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>508700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>506700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>581100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>547700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>557900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>458500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>498500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>454400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>381700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>363500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>367100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>366400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>343000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>350100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>369600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>324100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>313900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>309800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>281900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>268500</v>
       </c>
-      <c r="AI66" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="AJ66" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="AK66" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6470,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6575,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6682,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6607,7 +6775,7 @@
         <v>0</v>
       </c>
       <c r="AF70" s="3">
-        <v>1465400</v>
+        <v>0</v>
       </c>
       <c r="AG70" s="3">
         <v>1465400</v>
@@ -6616,13 +6784,16 @@
         <v>1465400</v>
       </c>
       <c r="AI70" s="3">
-        <v>0</v>
+        <v>1465400</v>
       </c>
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +6896,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E72" s="3">
         <v>55100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>128700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-148400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-240500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-279200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-288200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2135600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2166200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-2175100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-2150300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-2351400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-2358200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-2323200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-2114700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-2132100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-2067000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-2023900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-2018600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-2193300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-2287300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-2356700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-2335000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-2542900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-2448700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-2347900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-2206700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-2171000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-2046300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-886800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-845400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-892400</v>
       </c>
-      <c r="AI72" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="AJ72" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="AK72" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7110,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7217,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7324,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2893900</v>
+      </c>
+      <c r="E76" s="3">
         <v>2850600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4745200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4825000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4812000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4688500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4751200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2893900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3198100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3143800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3090700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2806600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2693100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3059700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3281700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3144500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3136100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3099700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3038700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2698400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2503900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2328800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2242400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1934600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1906600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1938500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2023700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1956400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2073200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-634000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>-594600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>-644100</v>
       </c>
-      <c r="AI76" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="AJ76" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="AK76" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7538,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>-46700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-73600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>277100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>92100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>38800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>8900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1847500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>30600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>8900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-24800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>201200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>6700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-34900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-208600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>17500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-65200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-43100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-5300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>174700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>94000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>69400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-21700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>207800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-94200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-100700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-141200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-35700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-124700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-1159500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-41400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>47000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-18900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-38400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-52700</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,67 +7798,68 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E83" s="3">
         <v>4000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>6100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5400</v>
-      </c>
-      <c r="G83" s="3">
-        <v>4900</v>
       </c>
       <c r="H83" s="3">
         <v>4900</v>
       </c>
       <c r="I83" s="3">
+        <v>4900</v>
+      </c>
+      <c r="J83" s="3">
         <v>5300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>6200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>19600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>10500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>9100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>7200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>19600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>10500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>9100</v>
-      </c>
-      <c r="T83" s="3">
-        <v>7200</v>
       </c>
       <c r="U83" s="3">
         <v>7200</v>
       </c>
       <c r="V83" s="3">
-        <v>6800</v>
+        <v>7200</v>
       </c>
       <c r="W83" s="3">
         <v>6800</v>
@@ -7669,43 +7868,46 @@
         <v>6800</v>
       </c>
       <c r="Y83" s="3">
+        <v>6800</v>
+      </c>
+      <c r="Z83" s="3">
         <v>7800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>8900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>8500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>11700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>8300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>7300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>6500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>5700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>5400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>5100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>5500</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8010,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8117,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8224,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8331,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8438,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>292900</v>
+      </c>
+      <c r="E89" s="3">
         <v>328000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>391200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>321700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>207700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>363700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>254000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>248000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>106400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>356100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>258300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>108500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>62700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>183500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>58300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>77500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>120100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>213400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>211800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>165700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>104800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>270600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>100700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-92600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-36500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>57300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>9600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>7500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-49500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>33100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-18800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-12700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-42400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,112 +8586,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-23000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-16300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-10800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-11000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-7300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-12100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-8000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-13000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-6900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-4300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-7000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-13400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-8500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-8200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-3700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-4600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-4100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-5300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8798,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,112 +8905,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>45900</v>
+      </c>
+      <c r="E94" s="3">
         <v>112900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>33700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-94100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-86100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>11900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>31800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-38500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-211200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>21700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-40200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-32600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>14200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-66100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>13700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-125200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>49400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-29700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>50700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-11800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-35100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-98900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-164600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>158000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>57800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-383700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-258100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>59100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-3800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>44900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-18600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>87000</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,8 +9053,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8864,8 +9098,8 @@
       <c r="P96" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -8924,8 +9158,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9265,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9372,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,316 +9479,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-294500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1032100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-586700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-312200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-158300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-260700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-183100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-551700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-150600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-83000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-87500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-79300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-501400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-158600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-55400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-59700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-34900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>4300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>3000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>5600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>9300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>13300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>30500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-23700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-9500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-123500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1264300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-3200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-300</v>
-      </c>
-      <c r="AI100" s="3">
-        <v>400</v>
       </c>
       <c r="AJ100" s="3">
         <v>400</v>
       </c>
+      <c r="AK100" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E101" s="3">
         <v>900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>2100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-2300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>2100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-2300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>300</v>
-      </c>
-      <c r="U101" s="3">
-        <v>-400</v>
       </c>
       <c r="V101" s="3">
         <v>-400</v>
       </c>
       <c r="W101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="X101" s="3">
         <v>100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>400</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>100</v>
       </c>
       <c r="AA101" s="3">
         <v>100</v>
       </c>
       <c r="AB101" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC101" s="3">
         <v>-200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-200</v>
       </c>
-      <c r="AE101" s="3">
-        <v>0</v>
-      </c>
       <c r="AF101" s="3">
         <v>0</v>
       </c>
       <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
         <v>-100</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>44400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-591300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-161800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-84500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-35300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>115900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>100800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-341400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-256100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>269400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>193500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-11400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-471400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>40200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-61100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>29800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-42400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>264200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>186000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>219000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>98600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>244500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>15500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-226600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>121100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>91200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-383400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-374200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1273900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>26100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>23200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-12300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-60700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>101000</v>
       </c>
     </row>
